--- a/ig/main/ValueSet-1.2.250.1.213.1.1.5.660.xlsx
+++ b/ig/main/ValueSet-1.2.250.1.213.1.1.5.660.xlsx
@@ -7,12 +7,12 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from TRE_R308_TAASIP" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from unknown" r:id="rId5" sheetId="3"/>
-    <sheet name="Include from TRE_R308_TAASIP 2" r:id="rId6" sheetId="4"/>
-    <sheet name="Include from unknown 2" r:id="rId7" sheetId="5"/>
-    <sheet name="Include from unknown 3" r:id="rId8" sheetId="6"/>
-    <sheet name="Include from unknown 4" r:id="rId9" sheetId="7"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Include #2" r:id="rId6" sheetId="4"/>
+    <sheet name="Include #3" r:id="rId7" sheetId="5"/>
+    <sheet name="Include #4" r:id="rId8" sheetId="6"/>
+    <sheet name="Include #5" r:id="rId9" sheetId="7"/>
   </sheets>
 </workbook>
 </file>
